--- a/组合介绍/report_assets/factors/workbooks/5-Microsoft_Excel_Worksheet5.xlsx
+++ b/组合介绍/report_assets/factors/workbooks/5-Microsoft_Excel_Worksheet5.xlsx
@@ -134,10 +134,10 @@
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="true" applyProtection="false" borderId="2" fillId="0" fontId="1" numFmtId="164" xfId="0">
+    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0">
@@ -478,72 +478,72 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="str">
+      <c r="A2" s="2" t="str">
         <v>G6-I9-M3</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="1">
         <v>0.39</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="1">
         <v>0.634</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>0.78</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="str">
+      <c r="A3" s="2" t="str">
         <v>G6-I12-M3</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="1">
         <v>0.366</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="1">
         <v>0.634</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>0.78</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="str">
+      <c r="A4" s="2" t="str">
         <v>G1-I9-M3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>0.341</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>0.634</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>0.78</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="str">
+      <c r="A5" s="2" t="str">
         <v>G3-I12-M3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="1">
         <v>0.341</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>0.634</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>0.805</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="str">
+      <c r="A6" s="2" t="str">
         <v>G12-I12-M12</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="1">
         <v>0.341</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="1">
         <v>0.634</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>0.805</v>
       </c>
     </row>
